--- a/hasil/hasil_perbandingan.xlsx
+++ b/hasil/hasil_perbandingan.xlsx
@@ -617,10 +617,10 @@
         <v>0.06</v>
       </c>
       <c r="I3" t="n">
-        <v>24.84</v>
+        <v>22.89</v>
       </c>
       <c r="J3" t="n">
-        <v>2.46</v>
+        <v>1.8</v>
       </c>
       <c r="K3" t="n">
         <v>0.98</v>
@@ -683,10 +683,10 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>47.83</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>34.85</v>
+        <v>24.22</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -743,16 +743,16 @@
         <v>650.65</v>
       </c>
       <c r="G5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="I5" t="n">
-        <v>55.6</v>
+        <v>54.29</v>
       </c>
       <c r="J5" t="n">
-        <v>3.43</v>
+        <v>2.79</v>
       </c>
       <c r="K5" t="n">
         <v>0.98</v>
@@ -878,13 +878,13 @@
         <v>0.28</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="I7" t="n">
-        <v>51.25</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>21.1</v>
+        <v>25.47</v>
       </c>
       <c r="K7" t="n">
         <v>229.95</v>
@@ -944,13 +944,13 @@
         <v>0.28</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="I8" t="n">
-        <v>56.26</v>
+        <v>54.29</v>
       </c>
       <c r="J8" t="n">
-        <v>3.51</v>
+        <v>2.79</v>
       </c>
       <c r="K8" t="n">
         <v>229.95</v>
@@ -2782,10 +2782,10 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>24.8361</v>
+        <v>22.8898</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4569</v>
+        <v>1.8035</v>
       </c>
     </row>
     <row r="4">
@@ -2801,10 +2801,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>47.83</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>34.8477</v>
+        <v>24.2181</v>
       </c>
     </row>
     <row r="5">
@@ -2814,16 +2814,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.288</v>
+        <v>0.2781</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0314</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>55.6008</v>
+        <v>54.29</v>
       </c>
       <c r="E5" t="n">
-        <v>3.4274</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="6">
@@ -2855,13 +2855,13 @@
         <v>0.2781</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0419</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>51.2512</v>
+        <v>70.31780000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>21.1041</v>
+        <v>25.4709</v>
       </c>
     </row>
     <row r="8">
@@ -2874,13 +2874,13 @@
         <v>0.2781</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0419</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>56.2562</v>
+        <v>54.29</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5067</v>
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>
